--- a/Approval_scenario.xlsx
+++ b/Approval_scenario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Divyesh\IFC\IFC_Prisma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CF20528-056D-4E90-A65A-4303205EA839}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800EEEAB-5938-48C0-845E-E8C2B0330D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{069BF09D-1EB0-44AE-A074-AC094321DB43}"/>
   </bookViews>

--- a/Approval_scenario.xlsx
+++ b/Approval_scenario.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Divyesh\IFC\IFC_Prisma\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{800EEEAB-5938-48C0-845E-E8C2B0330D1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D28271B9-C976-4BE0-9619-BCD5EB65F3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{069BF09D-1EB0-44AE-A074-AC094321DB43}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <si>
     <t>Approve/Reject</t>
   </si>
@@ -72,14 +72,82 @@
   </si>
   <si>
     <t>Action required by coordinator/process-owner. Either provide mitigation plan or compensatory RACM/doc.</t>
+  </si>
+  <si>
+    <t>User-Type</t>
+  </si>
+  <si>
+    <t>User/Process-owner</t>
+  </si>
+  <si>
+    <t>Created by Company Coordinator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Will be assigned RACMs by company co. </t>
+  </si>
+  <si>
+    <t>Their purpose is to attach required documents and submit RACMs for approval</t>
+  </si>
+  <si>
+    <t>If Rejected they need to provide different documents and re-submit for approval</t>
+  </si>
+  <si>
+    <t>User can submit deficiency response if RACM is marked ineffective by the approver.</t>
+  </si>
+  <si>
+    <t>User can also suggest changes in RACM to respective company coordinator.</t>
+  </si>
+  <si>
+    <t>Company Coordinator</t>
+  </si>
+  <si>
+    <t>Can create RACM either manually or by excel bulk upload option.</t>
+  </si>
+  <si>
+    <t>Will be created at the time of company creation by siteadmin.</t>
+  </si>
+  <si>
+    <t>Can add company specific business processes.</t>
+  </si>
+  <si>
+    <t>Can create units of the company as well as coordinators and approvers for the different units of the company.</t>
+  </si>
+  <si>
+    <t>Responsible for providing sample documents, setting due date and process owner assignment of RACMs</t>
+  </si>
+  <si>
+    <t>Can submit deficiency response if RACM is marked ineffective by the approver.</t>
+  </si>
+  <si>
+    <t>Approver</t>
+  </si>
+  <si>
+    <t>Will be created by company coordinator and assigned to a single or multiple units of company</t>
+  </si>
+  <si>
+    <t>Can Approve/Reject the RACMs (For more info look at the bottom of the sheet for approval cases)</t>
+  </si>
+  <si>
+    <t>Responsible for reviewing deficiency responses and pass judgement</t>
+  </si>
+  <si>
+    <t>Auditor</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -107,8 +175,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -423,63 +495,158 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7344510A-1B15-4CED-8360-74A45E8617FA}">
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C51"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="26.7109375" customWidth="1"/>
-    <col min="2" max="2" width="32.5703125" customWidth="1"/>
-    <col min="3" max="3" width="96.5703125" customWidth="1"/>
+    <col min="2" max="2" width="77" customWidth="1"/>
+    <col min="3" max="3" width="55.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B5" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B6" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="30" x14ac:dyDescent="0.25">
+      <c r="B8" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" ht="32.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" ht="42" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" ht="27.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B45" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B47" t="s">
         <v>3</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C47" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
         <v>2</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B48" t="s">
         <v>5</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C48" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="49" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
         <v>2</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B49" t="s">
         <v>7</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C49" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="51" spans="1:3" ht="30" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
         <v>8</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B51" t="s">
         <v>9</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C51" s="1" t="s">
         <v>6</v>
       </c>
     </row>
